--- a/5/search/FY4_Missile2_results/best_solution.xlsx
+++ b/5/search/FY4_Missile2_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="B2" t="n">
-        <v>100.8</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>11366.09793898997</v>
+        <v>10703.75623284459</v>
       </c>
       <c r="F2" t="n">
-        <v>1281.4923388945</v>
+        <v>1592.255434835027</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>11823.72036272743</v>
+        <v>9815.024931378373</v>
       </c>
       <c r="I2" t="n">
-        <v>383.3577625126252</v>
+        <v>369.0217393401063</v>
       </c>
       <c r="J2" t="n">
-        <v>1310</v>
+        <v>1094.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
